--- a/4P_Index_Arrete_09311_Huiles_Usees.xlsx
+++ b/4P_Index_Arrete_09311_Huiles_Usees.xlsx
@@ -625,11 +625,11 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>use, collection, disposal</t>
+          <t>consumption, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
@@ -722,11 +722,11 @@
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>use, collection, disposal</t>
+          <t>consumption, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Disposal</t>
+          <t>End of life</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>use, collection, disposal</t>
+          <t>consumption, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
